--- a/astro-site/public/dl/pastry-shop-checklist-templates/12-bakery-allergen-chart.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/12-bakery-allergen-chart.xlsx
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>●</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
@@ -1457,7 +1457,7 @@
       <c r="P8" s="14" t="n"/>
       <c r="Q8" s="15">
         <f>COUNTIF(C8:P8,"●")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R8" s="16" t="n"/>
       <c r="S8" s="17" t="n"/>
@@ -2398,14 +2398,14 @@
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>●</t>
         </is>
       </c>
       <c r="O24" s="14" t="n"/>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="15">
         <f>COUNTIF(C24:P24,"●")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="R24" s="16" t="n"/>
       <c r="S24" s="17" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="V24" s="19" t="inlineStr">
         <is>
-          <t>Sulfites: if the raisins or candied peel contain sulfites (10 ppm or more), declare them as an ingredient, not as a trace.</t>
+          <t>Sulfites: candied peel and raisins are usually sulfited (10 ppm or more): declare them as an ingredient (●), not as a trace.</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       <c r="H28" s="14" t="n"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>●</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
@@ -2633,7 +2633,7 @@
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="15">
         <f>COUNTIF(C28:P28,"●")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="R28" s="16" t="n"/>
       <c r="S28" s="17" t="n"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V28" s="19" t="inlineStr">
         <is>
-          <t>Sesame: some polvorones contain sesame — check yours. Milk: the proposed profile assumes lard or shortening; with butter, milk is ●.</t>
+          <t>Milk: Mexican wedding cookies are usually made with butter (●); only with lard or shortening is it ○. Sesame: some polvorones contain it — check yours.</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="I53" s="24">
         <f>COUNTIF(I5:I51,"●")</f>
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="J53" s="24">
         <f>COUNTIF(J5:J51,"●")</f>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="N53" s="24">
         <f>COUNTIF(N5:N51,"●")</f>
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="O53" s="24">
         <f>COUNTIF(O5:O51,"●")</f>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I54" s="27">
         <f>COUNTIF(I5:I51,"○")</f>
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="J54" s="27">
         <f>COUNTIF(J5:J51,"○")</f>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="N54" s="27">
         <f>COUNTIF(N5:N51,"○")</f>
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="O54" s="27">
         <f>COUNTIF(O5:O51,"○")</f>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H9" s="31" t="str">
         <f>IF('Allergen Matrix'!I8="","",'Allergen Matrix'!I8)</f>
-        <v>○</v>
+        <v>●</v>
       </c>
       <c r="I9" s="31" t="str">
         <f>IF('Allergen Matrix'!J8="","",'Allergen Matrix'!J8)</f>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="M25" s="31" t="str">
         <f>IF('Allergen Matrix'!N24="","",'Allergen Matrix'!N24)</f>
-        <v>○</v>
+        <v>●</v>
       </c>
       <c r="N25" s="31">
         <f>IF('Allergen Matrix'!O24="","",'Allergen Matrix'!O24)</f>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="H29" s="31" t="str">
         <f>IF('Allergen Matrix'!I28="","",'Allergen Matrix'!I28)</f>
-        <v>○</v>
+        <v>●</v>
       </c>
       <c r="I29" s="31" t="str">
         <f>IF('Allergen Matrix'!J28="","",'Allergen Matrix'!J28)</f>
@@ -7100,7 +7100,7 @@
     <row r="54" ht="21.8" customHeight="1">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>Our kitchen handles, among others, wheat (gluten), eggs, milk, tree nuts, soy and sesame, so cross-contact is possible. This notice complements the written information: it does not replace it.</t>
+          <t>Our kitchen handles, among others, wheat (gluten), eggs, milk, tree nuts, soy, sesame and fish (replace with your own list), so cross-contact is possible. This notice complements the written information: it does not replace it.</t>
         </is>
       </c>
       <c r="B54" s="48" t="n"/>
@@ -7211,7 +7211,7 @@
     <row r="7" ht="23.8" customHeight="1">
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Our kitchen handles, among others, wheat (gluten), eggs, milk, tree nuts, soy and sesame, so cross-contact is possible. This notice complements the written information: it does not replace it.</t>
+          <t>Our kitchen handles, among others, wheat (gluten), eggs, milk, tree nuts, soy, sesame and fish (replace with your own list), so cross-contact is possible. This notice complements the written information: it does not replace it.</t>
         </is>
       </c>
       <c r="C7" s="48" t="n"/>
@@ -7500,7 +7500,7 @@
     <row r="2" ht="30.4" customHeight="1">
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>Fill in, print on card stock and cut along the edge. Abbreviate the allergens: W wheat · E eggs · M milk · TN tree nuts · S soy · SE sesame · SU sulfites.</t>
+          <t>Fill in, print on card stock and cut along the edge. Abbreviate the allergens: W wheat · E eggs · M milk · TN tree nuts · P peanuts · S soy · SE sesame · F fish · SH shellfish · SU sulfites.</t>
         </is>
       </c>
     </row>
